--- a/output/pdf_financials_xlsx/PPR.xlsx
+++ b/output/pdf_financials_xlsx/PPR.xlsx
@@ -4855,34 +4855,34 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-21.25</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-28.741</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-13.385</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.646</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.682</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>0.793</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>0.751</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="119">
@@ -18112,7 +18112,11 @@
           <t>Exploration and evaluation expense 6</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -20418,7 +20422,11 @@
           <t>Exploration and evaluation expense 5</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr"/>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
@@ -21760,7 +21768,11 @@
           <t>Exploration and evaluation expenditures 5</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E254" s="5" t="n">
         <v>-21.25</v>
       </c>
@@ -25638,7 +25650,11 @@
           <t>Exploration and evaluation expense 7</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -26806,7 +26822,11 @@
           <t>Exploration and evaluation expenditures 7</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -28764,7 +28784,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PPR.xlsx
+++ b/output/pdf_financials_xlsx/PPR.xlsx
@@ -769,16 +769,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>106.923</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>88.73399999999999</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>122.619</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>107.028</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
@@ -792,13 +792,13 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>91.08799999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>54.646</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>50.998</v>
       </c>
     </row>
     <row r="11">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>47.087</v>
+        <v>-59.836</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>28.324</v>
+        <v>-60.41</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>73.31100000000001</v>
+        <v>-33.717</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>75.018</v>
@@ -833,7 +833,7 @@
         <v>81.974</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>68.60899999999999</v>
+        <v>-22.479</v>
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
@@ -876,13 +876,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.114</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.202</v>
       </c>
     </row>
     <row r="13">
@@ -1521,13 +1521,13 @@
         <v>-2.402</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-21.42</v>
+        <v>-21.306</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-16.307</v>
+        <v>-16.067</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-13.749</v>
+        <v>-13.547</v>
       </c>
     </row>
     <row r="28">
@@ -1599,13 +1599,13 @@
         <v>19.133</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.887</v>
+        <v>-4.773</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-7.328</v>
+        <v>-7.088</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-13.749</v>
+        <v>-13.547</v>
       </c>
     </row>
     <row r="30">
@@ -1640,7 +1640,7 @@
         <v>23.34032742088955</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-7.12297220481278</v>
+        <v>-6.956813246075589</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -1760,25 +1760,25 @@
         <v>3.564</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.867</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.873</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.851</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6.565</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.835</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>4.722</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>7.378</v>
       </c>
     </row>
     <row r="35">
@@ -1834,25 +1834,25 @@
         <v>3.564</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.867</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.873</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.851</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>6.565</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.835</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>4.722</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>7.378</v>
       </c>
     </row>
     <row r="37">
@@ -2278,25 +2278,25 @@
         <v>7.845</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>18.18</v>
+        <v>16.313</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>11.083</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>9.465</v>
+        <v>7.614</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>15.195</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>59.793</v>
+        <v>57.958</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>12.304</v>
+        <v>7.582</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>15.08</v>
+        <v>7.702</v>
       </c>
     </row>
     <row r="49">
@@ -5091,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-3.803</v>
       </c>
       <c r="G124" s="3" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-3.803</v>
       </c>
       <c r="G125" s="3" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -26496,7 +26496,11 @@
           <t>Finance lease payments 12</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -32832,7 +32836,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E424" s="5" t="n">
@@ -34578,7 +34582,7 @@
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
@@ -37406,7 +37410,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -39538,7 +39542,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -40762,7 +40766,7 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -41022,7 +41026,7 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -42180,7 +42184,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -42442,7 +42446,7 @@
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -43800,7 +43804,7 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E594" s="5" t="n">

--- a/output/pdf_financials_xlsx/PPR.xlsx
+++ b/output/pdf_financials_xlsx/PPR.xlsx
@@ -1549,7 +1549,7 @@
         <v>29.686</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>39.826</v>
+        <v>2.743</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
@@ -1557,16 +1557,16 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>21.535</v>
+        <v>1.851</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>16.533</v>
+        <v>16.993</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>8.978999999999999</v>
+        <v>9.308999999999999</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>10.378</v>
       </c>
     </row>
     <row r="29">
@@ -1588,7 +1588,7 @@
         <v>-3.279</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.747</v>
+        <v>-30.336</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1596,16 +1596,16 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19.133</v>
+        <v>-0.551</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.773</v>
+        <v>-4.313</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-7.088</v>
+        <v>-6.758</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-13.547</v>
+        <v>-3.169</v>
       </c>
     </row>
     <row r="30">
@@ -1629,7 +1629,7 @@
         <v>-4.472725784670787</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>8.993841478045269</v>
+        <v>-40.43829480924578</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -1637,10 +1637,10 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>23.34032742088955</v>
+        <v>-0.6721643447922512</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-6.956813246075589</v>
+        <v>-6.286347272223761</v>
       </c>
       <c r="J30" s="1" t="inlineStr">
         <is>
@@ -4201,22 +4201,22 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2.743</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>1.638</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>1.851</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>9.308999999999999</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>10.378</v>
       </c>
     </row>
     <row r="101">
@@ -4633,10 +4633,10 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -17986,7 +17986,11 @@
           <t>Depletion and depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -18050,7 +18054,11 @@
           <t>Depreciation on right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -22346,7 +22354,11 @@
           <t>Depreciation on right-of-use asset 8</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E263" t="inlineStr">
         <is>
           <t>-</t>
@@ -24026,7 +24038,11 @@
           <t>Depreciation on right-of-use asset 7</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -25584,7 +25600,11 @@
           <t>Depreciation on right-of-use asset 9</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E313" t="inlineStr">
         <is>
           <t>-</t>
@@ -31294,7 +31314,11 @@
           <t>Proceeds on sale of property and equipment</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E400" s="5" t="n">
         <v>0.15</v>
       </c>
@@ -32204,7 +32228,11 @@
           <t>Depletion and depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -32326,7 +32354,11 @@
           <t>Depreciation on right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -34962,7 +34994,11 @@
           <t>Depletion and depreciation of property and equipment 6</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -38440,7 +38476,11 @@
           <t>Depreciation on right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E511" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PPR.xlsx
+++ b/output/pdf_financials_xlsx/PPR.xlsx
@@ -8462,7 +8462,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -25930,7 +25934,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -27758,7 +27766,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
